--- a/Catch models/management_table_macarellus_cmsy.xlsx
+++ b/Catch models/management_table_macarellus_cmsy.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="61">
   <si>
     <t>stock_group</t>
   </si>
@@ -52,154 +52,151 @@
     <t>NN_CMSY_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.48 (0.22-0.79)</t>
-  </si>
-  <si>
-    <t>0.88 (0.38-4.24)</t>
+    <t>0.39 (0.32-0.48)</t>
+  </si>
+  <si>
+    <t>1.60 (1.01-2.43)</t>
+  </si>
+  <si>
+    <t>Overfished and overfishing</t>
+  </si>
+  <si>
+    <t>NN_CMSY_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.38 (0.33-0.44)</t>
+  </si>
+  <si>
+    <t>1.47 (1.06-1.98)</t>
+  </si>
+  <si>
+    <t>NN_CMSY_lower resilience</t>
+  </si>
+  <si>
+    <t>0.36 (0.21-0.59)</t>
+  </si>
+  <si>
+    <t>1.53 (0.55-4.45)</t>
+  </si>
+  <si>
+    <t>NN_CMSY_Non-informative_r</t>
+  </si>
+  <si>
+    <t>0.37 (0.25-0.50)</t>
+  </si>
+  <si>
+    <t>1.77 (0.88-3.46)</t>
+  </si>
+  <si>
+    <t>Target_switch_Euler-lotka methods</t>
+  </si>
+  <si>
+    <t>0.50 (0.38-0.74)</t>
+  </si>
+  <si>
+    <t>0.99 (0.56-1.63)</t>
   </si>
   <si>
     <t>Overfished but not overfishing</t>
   </si>
   <si>
-    <t>NN_CMSY_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.40 (0.17-0.73)</t>
-  </si>
-  <si>
-    <t>1.09 (0.43-6.38)</t>
-  </si>
-  <si>
-    <t>Overfished and overfishing</t>
-  </si>
-  <si>
-    <t>NN_CMSY_lower resilience</t>
-  </si>
-  <si>
-    <t>0.49 (0.25-0.83)</t>
-  </si>
-  <si>
-    <t>0.72 (0.32-2.81)</t>
-  </si>
-  <si>
-    <t>NN_CMSY_Non-informative_r</t>
-  </si>
-  <si>
-    <t>0.46 (0.22-0.74)</t>
-  </si>
-  <si>
-    <t>0.97 (0.42-4.55)</t>
-  </si>
-  <si>
-    <t>Target_switch_Euler-lotka methods</t>
-  </si>
-  <si>
-    <t>0.96 (0.52-1.36)</t>
-  </si>
-  <si>
-    <t>0.36 (0.19-0.84)</t>
-  </si>
-  <si>
     <t>Target_switch_Higher resilience</t>
   </si>
   <si>
-    <t>0.96 (0.52-1.38)</t>
-  </si>
-  <si>
-    <t>0.34 (0.19-0.77)</t>
+    <t>0.41 (0.34-0.56)</t>
+  </si>
+  <si>
+    <t>1.24 (0.73-1.74)</t>
   </si>
   <si>
     <t>Target_switch_lower resilience</t>
   </si>
   <si>
-    <t>0.99 (0.56-1.38)</t>
-  </si>
-  <si>
-    <t>0.32 (0.16-0.73)</t>
+    <t>0.63 (0.39-0.91)</t>
+  </si>
+  <si>
+    <t>0.63 (0.33-1.41)</t>
   </si>
   <si>
     <t>Target_switch_Non-informative_r</t>
   </si>
   <si>
-    <t>0.98 (0.56-1.38)</t>
-  </si>
-  <si>
-    <t>0.35 (0.18-0.80)</t>
+    <t>0.55 (0.38-0.80)</t>
+  </si>
+  <si>
+    <t>0.88 (0.48-1.68)</t>
   </si>
   <si>
     <t>Uninformative_bk_Euler-lotka methods</t>
   </si>
   <si>
-    <t>1.07 (0.32-1.65)</t>
-  </si>
-  <si>
-    <t>0.31 (0.14-2.12)</t>
-  </si>
-  <si>
-    <t>Neither overfishing nor overfished</t>
+    <t>0.53 (0.38-0.82)</t>
+  </si>
+  <si>
+    <t>0.91 (0.47-1.66)</t>
   </si>
   <si>
     <t>Uninformative_bk_Higher resilience</t>
   </si>
   <si>
-    <t>1.07 (0.40-1.72)</t>
-  </si>
-  <si>
-    <t>0.30 (0.13-1.17)</t>
+    <t>0.43 (0.35-0.68)</t>
+  </si>
+  <si>
+    <t>1.14 (0.55-1.69)</t>
   </si>
   <si>
     <t>Uninformative_bk_lower resilience</t>
   </si>
   <si>
-    <t>1.07 (0.54-1.70)</t>
-  </si>
-  <si>
-    <t>0.29 (0.13-0.77)</t>
+    <t>0.56 (0.28-0.91)</t>
+  </si>
+  <si>
+    <t>0.74 (0.35-2.66)</t>
   </si>
   <si>
     <t>Uninformative_bk_Non-informative_r</t>
   </si>
   <si>
-    <t>1.06 (0.32-1.64)</t>
-  </si>
-  <si>
-    <t>0.32 (0.14-2.00)</t>
+    <t>0.56 (0.31-0.90)</t>
+  </si>
+  <si>
+    <t>0.76 (0.38-2.27)</t>
   </si>
   <si>
     <t>zBRT_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.89 (0.46-1.42)</t>
-  </si>
-  <si>
-    <t>0.40 (0.18-1.04)</t>
+    <t>0.42 (0.33-0.64)</t>
+  </si>
+  <si>
+    <t>1.33 (0.68-2.24)</t>
   </si>
   <si>
     <t>zBRT_Higher resilience</t>
   </si>
   <si>
-    <t>0.90 (0.38-1.45)</t>
-  </si>
-  <si>
-    <t>0.37 (0.17-1.31)</t>
+    <t>0.38 (0.33-0.46)</t>
+  </si>
+  <si>
+    <t>1.44 (1.03-1.93)</t>
   </si>
   <si>
     <t>zBRT_lower resilience</t>
   </si>
   <si>
-    <t>0.99 (0.49-1.45)</t>
-  </si>
-  <si>
-    <t>0.32 (0.16-0.83)</t>
+    <t>0.45 (0.23-0.75)</t>
+  </si>
+  <si>
+    <t>1.04 (0.44-3.98)</t>
   </si>
   <si>
     <t>zBRT_Non-informative_r</t>
   </si>
   <si>
-    <t>0.81 (0.39-1.33)</t>
-  </si>
-  <si>
-    <t>0.45 (0.20-1.43)</t>
+    <t>0.43 (0.28-0.69)</t>
+  </si>
+  <si>
+    <t>1.26 (0.55-2.92)</t>
   </si>
 </sst>
 </file>
@@ -588,10 +585,10 @@
         <v>2015</v>
       </c>
       <c r="E2">
-        <v>0.47698377173518</v>
+        <v>0.390652746625775</v>
       </c>
       <c r="F2">
-        <v>0.876553765176912</v>
+        <v>1.59877749054533</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -617,10 +614,10 @@
         <v>2015</v>
       </c>
       <c r="E3">
-        <v>0.401288034904273</v>
+        <v>0.379820103622074</v>
       </c>
       <c r="F3">
-        <v>1.09445345097222</v>
+        <v>1.4696346100241</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -629,7 +626,7 @@
         <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -640,22 +637,22 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>2015</v>
+      </c>
+      <c r="E4">
+        <v>0.356422876828626</v>
+      </c>
+      <c r="F4">
+        <v>1.5291469734584</v>
+      </c>
+      <c r="G4" t="s">
         <v>19</v>
       </c>
-      <c r="D4">
-        <v>2015</v>
-      </c>
-      <c r="E4">
-        <v>0.493715044655739</v>
-      </c>
-      <c r="F4">
-        <v>0.724595605258995</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>20</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
       </c>
       <c r="I4" t="s">
         <v>14</v>
@@ -669,22 +666,22 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>2015</v>
+      </c>
+      <c r="E5">
+        <v>0.367536453818028</v>
+      </c>
+      <c r="F5">
+        <v>1.77176778721381</v>
+      </c>
+      <c r="G5" t="s">
         <v>22</v>
       </c>
-      <c r="D5">
-        <v>2015</v>
-      </c>
-      <c r="E5">
-        <v>0.457431897118929</v>
-      </c>
-      <c r="F5">
-        <v>0.96577360942505</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>23</v>
-      </c>
-      <c r="H5" t="s">
-        <v>24</v>
       </c>
       <c r="I5" t="s">
         <v>14</v>
@@ -698,25 +695,25 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>2015</v>
+      </c>
+      <c r="E6">
+        <v>0.498562553199792</v>
+      </c>
+      <c r="F6">
+        <v>0.988186431302391</v>
+      </c>
+      <c r="G6" t="s">
         <v>25</v>
       </c>
-      <c r="D6">
-        <v>2015</v>
-      </c>
-      <c r="E6">
-        <v>0.960426658715316</v>
-      </c>
-      <c r="F6">
-        <v>0.359269345620606</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>26</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>27</v>
-      </c>
-      <c r="I6" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -733,10 +730,10 @@
         <v>2015</v>
       </c>
       <c r="E7">
-        <v>0.962083033749682</v>
+        <v>0.412930381123275</v>
       </c>
       <c r="F7">
-        <v>0.341207409297429</v>
+        <v>1.23877944953271</v>
       </c>
       <c r="G7" t="s">
         <v>29</v>
@@ -762,10 +759,10 @@
         <v>2015</v>
       </c>
       <c r="E8">
-        <v>0.988315329022633</v>
+        <v>0.626768125232063</v>
       </c>
       <c r="F8">
-        <v>0.319734590044595</v>
+        <v>0.631016146815905</v>
       </c>
       <c r="G8" t="s">
         <v>32</v>
@@ -774,7 +771,7 @@
         <v>33</v>
       </c>
       <c r="I8" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -791,10 +788,10 @@
         <v>2015</v>
       </c>
       <c r="E9">
-        <v>0.980210569470792</v>
+        <v>0.5547898644602</v>
       </c>
       <c r="F9">
-        <v>0.354331734287307</v>
+        <v>0.879101026689028</v>
       </c>
       <c r="G9" t="s">
         <v>35</v>
@@ -803,7 +800,7 @@
         <v>36</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -820,10 +817,10 @@
         <v>2015</v>
       </c>
       <c r="E10">
-        <v>1.0683279736227</v>
+        <v>0.525809413467447</v>
       </c>
       <c r="F10">
-        <v>0.305839576437155</v>
+        <v>0.913401703819836</v>
       </c>
       <c r="G10" t="s">
         <v>38</v>
@@ -832,7 +829,7 @@
         <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -843,25 +840,25 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11">
+        <v>2015</v>
+      </c>
+      <c r="E11">
+        <v>0.430913538805287</v>
+      </c>
+      <c r="F11">
+        <v>1.13521660716966</v>
+      </c>
+      <c r="G11" t="s">
         <v>41</v>
       </c>
-      <c r="D11">
-        <v>2015</v>
-      </c>
-      <c r="E11">
-        <v>1.06781174426836</v>
-      </c>
-      <c r="F11">
-        <v>0.299627382839292</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>42</v>
       </c>
-      <c r="H11" t="s">
-        <v>43</v>
-      </c>
       <c r="I11" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -872,25 +869,25 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12">
+        <v>2015</v>
+      </c>
+      <c r="E12">
+        <v>0.55576389063904</v>
+      </c>
+      <c r="F12">
+        <v>0.736272301480813</v>
+      </c>
+      <c r="G12" t="s">
         <v>44</v>
       </c>
-      <c r="D12">
-        <v>2015</v>
-      </c>
-      <c r="E12">
-        <v>1.07399026341325</v>
-      </c>
-      <c r="F12">
-        <v>0.290206923808166</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>45</v>
       </c>
-      <c r="H12" t="s">
-        <v>46</v>
-      </c>
       <c r="I12" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -901,25 +898,25 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13">
+        <v>2015</v>
+      </c>
+      <c r="E13">
+        <v>0.555330098090342</v>
+      </c>
+      <c r="F13">
+        <v>0.75709810558839</v>
+      </c>
+      <c r="G13" t="s">
         <v>47</v>
       </c>
-      <c r="D13">
-        <v>2015</v>
-      </c>
-      <c r="E13">
-        <v>1.05835647537054</v>
-      </c>
-      <c r="F13">
-        <v>0.321399899080721</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>48</v>
       </c>
-      <c r="H13" t="s">
-        <v>49</v>
-      </c>
       <c r="I13" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -930,22 +927,22 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14">
+        <v>2015</v>
+      </c>
+      <c r="E14">
+        <v>0.424944418235067</v>
+      </c>
+      <c r="F14">
+        <v>1.33027666044184</v>
+      </c>
+      <c r="G14" t="s">
         <v>50</v>
       </c>
-      <c r="D14">
-        <v>2015</v>
-      </c>
-      <c r="E14">
-        <v>0.890150581076396</v>
-      </c>
-      <c r="F14">
-        <v>0.395068961850419</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>51</v>
-      </c>
-      <c r="H14" t="s">
-        <v>52</v>
       </c>
       <c r="I14" t="s">
         <v>14</v>
@@ -959,22 +956,22 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15">
+        <v>2015</v>
+      </c>
+      <c r="E15">
+        <v>0.38340840542639</v>
+      </c>
+      <c r="F15">
+        <v>1.44362458358269</v>
+      </c>
+      <c r="G15" t="s">
         <v>53</v>
       </c>
-      <c r="D15">
-        <v>2015</v>
-      </c>
-      <c r="E15">
-        <v>0.899186189314473</v>
-      </c>
-      <c r="F15">
-        <v>0.366297380132595</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>54</v>
-      </c>
-      <c r="H15" t="s">
-        <v>55</v>
       </c>
       <c r="I15" t="s">
         <v>14</v>
@@ -988,22 +985,22 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16">
+        <v>2015</v>
+      </c>
+      <c r="E16">
+        <v>0.451893332687842</v>
+      </c>
+      <c r="F16">
+        <v>1.04162900483522</v>
+      </c>
+      <c r="G16" t="s">
         <v>56</v>
       </c>
-      <c r="D16">
-        <v>2015</v>
-      </c>
-      <c r="E16">
-        <v>0.988332505002965</v>
-      </c>
-      <c r="F16">
-        <v>0.319788603171965</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>57</v>
-      </c>
-      <c r="H16" t="s">
-        <v>58</v>
       </c>
       <c r="I16" t="s">
         <v>14</v>
@@ -1017,22 +1014,22 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17">
+        <v>2015</v>
+      </c>
+      <c r="E17">
+        <v>0.432244941617663</v>
+      </c>
+      <c r="F17">
+        <v>1.26231063799676</v>
+      </c>
+      <c r="G17" t="s">
         <v>59</v>
       </c>
-      <c r="D17">
-        <v>2015</v>
-      </c>
-      <c r="E17">
-        <v>0.808280114365554</v>
-      </c>
-      <c r="F17">
-        <v>0.445043103667531</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>60</v>
-      </c>
-      <c r="H17" t="s">
-        <v>61</v>
       </c>
       <c r="I17" t="s">
         <v>14</v>

--- a/Catch models/management_table_macarellus_cmsy.xlsx
+++ b/Catch models/management_table_macarellus_cmsy.xlsx
@@ -52,10 +52,10 @@
     <t>NN_CMSY_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.39 (0.32-0.48)</t>
-  </si>
-  <si>
-    <t>1.60 (1.01-2.43)</t>
+    <t>0.32 (0.25-0.41)</t>
+  </si>
+  <si>
+    <t>1.97 (1.11-3.31)</t>
   </si>
   <si>
     <t>Overfished and overfishing</t>
@@ -64,139 +64,139 @@
     <t>NN_CMSY_Higher resilience</t>
   </si>
   <si>
-    <t>0.38 (0.33-0.44)</t>
-  </si>
-  <si>
-    <t>1.47 (1.06-1.98)</t>
+    <t>0.30 (0.26-0.35)</t>
+  </si>
+  <si>
+    <t>1.87 (1.33-2.53)</t>
   </si>
   <si>
     <t>NN_CMSY_lower resilience</t>
   </si>
   <si>
-    <t>0.36 (0.21-0.59)</t>
-  </si>
-  <si>
-    <t>1.53 (0.55-4.45)</t>
+    <t>0.37 (0.21-0.62)</t>
+  </si>
+  <si>
+    <t>1.28 (0.47-4.23)</t>
   </si>
   <si>
     <t>NN_CMSY_Non-informative_r</t>
   </si>
   <si>
-    <t>0.37 (0.25-0.50)</t>
-  </si>
-  <si>
-    <t>1.77 (0.88-3.46)</t>
+    <t>0.33 (0.24-0.48)</t>
+  </si>
+  <si>
+    <t>1.99 (0.92-3.86)</t>
   </si>
   <si>
     <t>Target_switch_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.50 (0.38-0.74)</t>
-  </si>
-  <si>
-    <t>0.99 (0.56-1.63)</t>
+    <t>0.36 (0.26-0.61)</t>
+  </si>
+  <si>
+    <t>1.56 (0.59-2.90)</t>
+  </si>
+  <si>
+    <t>Target_switch_Higher resilience</t>
+  </si>
+  <si>
+    <t>0.32 (0.27-0.41)</t>
+  </si>
+  <si>
+    <t>1.64 (1.04-2.31)</t>
+  </si>
+  <si>
+    <t>Target_switch_lower resilience</t>
+  </si>
+  <si>
+    <t>0.49 (0.27-0.83)</t>
+  </si>
+  <si>
+    <t>0.80 (0.35-2.70)</t>
   </si>
   <si>
     <t>Overfished but not overfishing</t>
   </si>
   <si>
-    <t>Target_switch_Higher resilience</t>
-  </si>
-  <si>
-    <t>0.41 (0.34-0.56)</t>
-  </si>
-  <si>
-    <t>1.24 (0.73-1.74)</t>
-  </si>
-  <si>
-    <t>Target_switch_lower resilience</t>
-  </si>
-  <si>
-    <t>0.63 (0.39-0.91)</t>
-  </si>
-  <si>
-    <t>0.63 (0.33-1.41)</t>
-  </si>
-  <si>
     <t>Target_switch_Non-informative_r</t>
   </si>
   <si>
-    <t>0.55 (0.38-0.80)</t>
-  </si>
-  <si>
-    <t>0.88 (0.48-1.68)</t>
+    <t>0.43 (0.29-0.71)</t>
+  </si>
+  <si>
+    <t>1.09 (0.48-2.49)</t>
   </si>
   <si>
     <t>Uninformative_bk_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.53 (0.38-0.82)</t>
-  </si>
-  <si>
-    <t>0.91 (0.47-1.66)</t>
+    <t>0.41 (0.27-0.65)</t>
+  </si>
+  <si>
+    <t>1.17 (0.55-2.72)</t>
   </si>
   <si>
     <t>Uninformative_bk_Higher resilience</t>
   </si>
   <si>
-    <t>0.43 (0.35-0.68)</t>
-  </si>
-  <si>
-    <t>1.14 (0.55-1.69)</t>
+    <t>0.40 (0.30-0.64)</t>
+  </si>
+  <si>
+    <t>1.09 (0.50-1.91)</t>
   </si>
   <si>
     <t>Uninformative_bk_lower resilience</t>
   </si>
   <si>
-    <t>0.56 (0.28-0.91)</t>
-  </si>
-  <si>
-    <t>0.74 (0.35-2.66)</t>
+    <t>0.57 (0.31-0.88)</t>
+  </si>
+  <si>
+    <t>0.65 (0.31-2.06)</t>
   </si>
   <si>
     <t>Uninformative_bk_Non-informative_r</t>
   </si>
   <si>
-    <t>0.56 (0.31-0.90)</t>
-  </si>
-  <si>
-    <t>0.76 (0.38-2.27)</t>
+    <t>0.50 (0.26-0.77)</t>
+  </si>
+  <si>
+    <t>0.87 (0.44-3.41)</t>
   </si>
   <si>
     <t>zBRT_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.42 (0.33-0.64)</t>
-  </si>
-  <si>
-    <t>1.33 (0.68-2.24)</t>
+    <t>0.35 (0.25-0.56)</t>
+  </si>
+  <si>
+    <t>1.60 (0.67-3.09)</t>
   </si>
   <si>
     <t>zBRT_Higher resilience</t>
   </si>
   <si>
-    <t>0.38 (0.33-0.46)</t>
-  </si>
-  <si>
-    <t>1.44 (1.03-1.93)</t>
+    <t>0.32 (0.27-0.39)</t>
+  </si>
+  <si>
+    <t>1.71 (1.11-2.42)</t>
   </si>
   <si>
     <t>zBRT_lower resilience</t>
   </si>
   <si>
-    <t>0.45 (0.23-0.75)</t>
-  </si>
-  <si>
-    <t>1.04 (0.44-3.98)</t>
+    <t>0.51 (0.28-0.78)</t>
+  </si>
+  <si>
+    <t>0.81 (0.37-2.60)</t>
   </si>
   <si>
     <t>zBRT_Non-informative_r</t>
   </si>
   <si>
-    <t>0.43 (0.28-0.69)</t>
-  </si>
-  <si>
-    <t>1.26 (0.55-2.92)</t>
+    <t>0.40 (0.25-0.68)</t>
+  </si>
+  <si>
+    <t>1.17 (0.46-3.17)</t>
   </si>
 </sst>
 </file>
@@ -585,10 +585,10 @@
         <v>2015</v>
       </c>
       <c r="E2">
-        <v>0.390652746625775</v>
+        <v>0.31564101541465</v>
       </c>
       <c r="F2">
-        <v>1.59877749054533</v>
+        <v>1.96816455576601</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -614,10 +614,10 @@
         <v>2015</v>
       </c>
       <c r="E3">
-        <v>0.379820103622074</v>
+        <v>0.303352631427009</v>
       </c>
       <c r="F3">
-        <v>1.4696346100241</v>
+        <v>1.8681160721803</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -643,10 +643,10 @@
         <v>2015</v>
       </c>
       <c r="E4">
-        <v>0.356422876828626</v>
+        <v>0.370280722813579</v>
       </c>
       <c r="F4">
-        <v>1.5291469734584</v>
+        <v>1.28404137134567</v>
       </c>
       <c r="G4" t="s">
         <v>19</v>
@@ -672,10 +672,10 @@
         <v>2015</v>
       </c>
       <c r="E5">
-        <v>0.367536453818028</v>
+        <v>0.331800607350954</v>
       </c>
       <c r="F5">
-        <v>1.77176778721381</v>
+        <v>1.99351237711982</v>
       </c>
       <c r="G5" t="s">
         <v>22</v>
@@ -701,10 +701,10 @@
         <v>2015</v>
       </c>
       <c r="E6">
-        <v>0.498562553199792</v>
+        <v>0.355265260926627</v>
       </c>
       <c r="F6">
-        <v>0.988186431302391</v>
+        <v>1.55760283043896</v>
       </c>
       <c r="G6" t="s">
         <v>25</v>
@@ -713,7 +713,7 @@
         <v>26</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -724,22 +724,22 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7">
+        <v>2015</v>
+      </c>
+      <c r="E7">
+        <v>0.324523936230862</v>
+      </c>
+      <c r="F7">
+        <v>1.64071462605627</v>
+      </c>
+      <c r="G7" t="s">
         <v>28</v>
       </c>
-      <c r="D7">
-        <v>2015</v>
-      </c>
-      <c r="E7">
-        <v>0.412930381123275</v>
-      </c>
-      <c r="F7">
-        <v>1.23877944953271</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>29</v>
-      </c>
-      <c r="H7" t="s">
-        <v>30</v>
       </c>
       <c r="I7" t="s">
         <v>14</v>
@@ -753,25 +753,25 @@
         <v>10</v>
       </c>
       <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8">
+        <v>2015</v>
+      </c>
+      <c r="E8">
+        <v>0.493045073236842</v>
+      </c>
+      <c r="F8">
+        <v>0.799173067176846</v>
+      </c>
+      <c r="G8" t="s">
         <v>31</v>
       </c>
-      <c r="D8">
-        <v>2015</v>
-      </c>
-      <c r="E8">
-        <v>0.626768125232063</v>
-      </c>
-      <c r="F8">
-        <v>0.631016146815905</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>32</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>33</v>
-      </c>
-      <c r="I8" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -788,10 +788,10 @@
         <v>2015</v>
       </c>
       <c r="E9">
-        <v>0.5547898644602</v>
+        <v>0.429424708773333</v>
       </c>
       <c r="F9">
-        <v>0.879101026689028</v>
+        <v>1.08792405246637</v>
       </c>
       <c r="G9" t="s">
         <v>35</v>
@@ -800,7 +800,7 @@
         <v>36</v>
       </c>
       <c r="I9" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -817,10 +817,10 @@
         <v>2015</v>
       </c>
       <c r="E10">
-        <v>0.525809413467447</v>
+        <v>0.406670666707175</v>
       </c>
       <c r="F10">
-        <v>0.913401703819836</v>
+        <v>1.17165489763336</v>
       </c>
       <c r="G10" t="s">
         <v>38</v>
@@ -829,7 +829,7 @@
         <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -846,10 +846,10 @@
         <v>2015</v>
       </c>
       <c r="E11">
-        <v>0.430913538805287</v>
+        <v>0.395638377269365</v>
       </c>
       <c r="F11">
-        <v>1.13521660716966</v>
+        <v>1.09227006120085</v>
       </c>
       <c r="G11" t="s">
         <v>41</v>
@@ -875,10 +875,10 @@
         <v>2015</v>
       </c>
       <c r="E12">
-        <v>0.55576389063904</v>
+        <v>0.567018154845911</v>
       </c>
       <c r="F12">
-        <v>0.736272301480813</v>
+        <v>0.647342879668618</v>
       </c>
       <c r="G12" t="s">
         <v>44</v>
@@ -887,7 +887,7 @@
         <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -904,10 +904,10 @@
         <v>2015</v>
       </c>
       <c r="E13">
-        <v>0.555330098090342</v>
+        <v>0.504707780365601</v>
       </c>
       <c r="F13">
-        <v>0.75709810558839</v>
+        <v>0.870895309456587</v>
       </c>
       <c r="G13" t="s">
         <v>47</v>
@@ -916,7 +916,7 @@
         <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -933,10 +933,10 @@
         <v>2015</v>
       </c>
       <c r="E14">
-        <v>0.424944418235067</v>
+        <v>0.350802761003074</v>
       </c>
       <c r="F14">
-        <v>1.33027666044184</v>
+        <v>1.59775147419397</v>
       </c>
       <c r="G14" t="s">
         <v>50</v>
@@ -962,10 +962,10 @@
         <v>2015</v>
       </c>
       <c r="E15">
-        <v>0.38340840542639</v>
+        <v>0.315722312545943</v>
       </c>
       <c r="F15">
-        <v>1.44362458358269</v>
+        <v>1.71464749361646</v>
       </c>
       <c r="G15" t="s">
         <v>53</v>
@@ -991,10 +991,10 @@
         <v>2015</v>
       </c>
       <c r="E16">
-        <v>0.451893332687842</v>
+        <v>0.50558228969071</v>
       </c>
       <c r="F16">
-        <v>1.04162900483522</v>
+        <v>0.814368661622665</v>
       </c>
       <c r="G16" t="s">
         <v>56</v>
@@ -1003,7 +1003,7 @@
         <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1020,10 +1020,10 @@
         <v>2015</v>
       </c>
       <c r="E17">
-        <v>0.432244941617663</v>
+        <v>0.398600571700721</v>
       </c>
       <c r="F17">
-        <v>1.26231063799676</v>
+        <v>1.17090878966136</v>
       </c>
       <c r="G17" t="s">
         <v>59</v>

--- a/Catch models/management_table_macarellus_cmsy.xlsx
+++ b/Catch models/management_table_macarellus_cmsy.xlsx
@@ -52,10 +52,10 @@
     <t>NN_CMSY_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.32 (0.25-0.41)</t>
-  </si>
-  <si>
-    <t>1.97 (1.11-3.31)</t>
+    <t>0.31 (0.24-0.39)</t>
+  </si>
+  <si>
+    <t>2.01 (1.19-3.36)</t>
   </si>
   <si>
     <t>Overfished and overfishing</t>
@@ -67,34 +67,34 @@
     <t>0.30 (0.26-0.35)</t>
   </si>
   <si>
-    <t>1.87 (1.33-2.53)</t>
+    <t>1.87 (1.34-2.54)</t>
   </si>
   <si>
     <t>NN_CMSY_lower resilience</t>
   </si>
   <si>
-    <t>0.37 (0.21-0.62)</t>
-  </si>
-  <si>
-    <t>1.28 (0.47-4.23)</t>
+    <t>0.35 (0.20-0.59)</t>
+  </si>
+  <si>
+    <t>1.51 (0.53-4.79)</t>
   </si>
   <si>
     <t>NN_CMSY_Non-informative_r</t>
   </si>
   <si>
-    <t>0.33 (0.24-0.48)</t>
-  </si>
-  <si>
-    <t>1.99 (0.92-3.86)</t>
+    <t>0.31 (0.21-0.43)</t>
+  </si>
+  <si>
+    <t>2.18 (1.00-4.88)</t>
   </si>
   <si>
     <t>Target_switch_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.36 (0.26-0.61)</t>
-  </si>
-  <si>
-    <t>1.56 (0.59-2.90)</t>
+    <t>0.35 (0.25-0.57)</t>
+  </si>
+  <si>
+    <t>1.55 (0.62-3.15)</t>
   </si>
   <si>
     <t>Target_switch_Higher resilience</t>
@@ -103,16 +103,16 @@
     <t>0.32 (0.27-0.41)</t>
   </si>
   <si>
-    <t>1.64 (1.04-2.31)</t>
+    <t>1.67 (1.00-2.35)</t>
   </si>
   <si>
     <t>Target_switch_lower resilience</t>
   </si>
   <si>
-    <t>0.49 (0.27-0.83)</t>
-  </si>
-  <si>
-    <t>0.80 (0.35-2.70)</t>
+    <t>0.50 (0.24-0.79)</t>
+  </si>
+  <si>
+    <t>0.77 (0.37-3.32)</t>
   </si>
   <si>
     <t>Overfished but not overfishing</t>
@@ -121,82 +121,82 @@
     <t>Target_switch_Non-informative_r</t>
   </si>
   <si>
-    <t>0.43 (0.29-0.71)</t>
-  </si>
-  <si>
-    <t>1.09 (0.48-2.49)</t>
+    <t>0.43 (0.23-0.70)</t>
+  </si>
+  <si>
+    <t>1.03 (0.45-3.41)</t>
   </si>
   <si>
     <t>Uninformative_bk_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.41 (0.27-0.65)</t>
-  </si>
-  <si>
-    <t>1.17 (0.55-2.72)</t>
+    <t>0.41 (0.26-0.71)</t>
+  </si>
+  <si>
+    <t>1.10 (0.45-2.78)</t>
   </si>
   <si>
     <t>Uninformative_bk_Higher resilience</t>
   </si>
   <si>
-    <t>0.40 (0.30-0.64)</t>
-  </si>
-  <si>
-    <t>1.09 (0.50-1.91)</t>
+    <t>0.40 (0.28-0.63)</t>
+  </si>
+  <si>
+    <t>1.07 (0.49-2.16)</t>
   </si>
   <si>
     <t>Uninformative_bk_lower resilience</t>
   </si>
   <si>
-    <t>0.57 (0.31-0.88)</t>
-  </si>
-  <si>
-    <t>0.65 (0.31-2.06)</t>
+    <t>0.54 (0.26-0.87)</t>
+  </si>
+  <si>
+    <t>0.68 (0.32-2.95)</t>
   </si>
   <si>
     <t>Uninformative_bk_Non-informative_r</t>
   </si>
   <si>
-    <t>0.50 (0.26-0.77)</t>
-  </si>
-  <si>
-    <t>0.87 (0.44-3.41)</t>
+    <t>0.47 (0.24-0.78)</t>
+  </si>
+  <si>
+    <t>0.86 (0.39-3.18)</t>
   </si>
   <si>
     <t>zBRT_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.35 (0.25-0.56)</t>
-  </si>
-  <si>
-    <t>1.60 (0.67-3.09)</t>
+    <t>0.34 (0.25-0.49)</t>
+  </si>
+  <si>
+    <t>1.59 (0.77-3.08)</t>
   </si>
   <si>
     <t>zBRT_Higher resilience</t>
   </si>
   <si>
-    <t>0.32 (0.27-0.39)</t>
-  </si>
-  <si>
-    <t>1.71 (1.11-2.42)</t>
+    <t>0.31 (0.26-0.38)</t>
+  </si>
+  <si>
+    <t>1.76 (1.14-2.49)</t>
   </si>
   <si>
     <t>zBRT_lower resilience</t>
   </si>
   <si>
-    <t>0.51 (0.28-0.78)</t>
-  </si>
-  <si>
-    <t>0.81 (0.37-2.60)</t>
+    <t>0.47 (0.26-0.75)</t>
+  </si>
+  <si>
+    <t>0.84 (0.38-2.81)</t>
   </si>
   <si>
     <t>zBRT_Non-informative_r</t>
   </si>
   <si>
-    <t>0.40 (0.25-0.68)</t>
-  </si>
-  <si>
-    <t>1.17 (0.46-3.17)</t>
+    <t>0.39 (0.24-0.64)</t>
+  </si>
+  <si>
+    <t>1.23 (0.51-3.30)</t>
   </si>
 </sst>
 </file>
@@ -585,10 +585,10 @@
         <v>2015</v>
       </c>
       <c r="E2">
-        <v>0.31564101541465</v>
+        <v>0.308984125884021</v>
       </c>
       <c r="F2">
-        <v>1.96816455576601</v>
+        <v>2.00862768631171</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -614,10 +614,10 @@
         <v>2015</v>
       </c>
       <c r="E3">
-        <v>0.303352631427009</v>
+        <v>0.302531754103853</v>
       </c>
       <c r="F3">
-        <v>1.8681160721803</v>
+        <v>1.87164011037127</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -643,10 +643,10 @@
         <v>2015</v>
       </c>
       <c r="E4">
-        <v>0.370280722813579</v>
+        <v>0.350896408871818</v>
       </c>
       <c r="F4">
-        <v>1.28404137134567</v>
+        <v>1.50649917333501</v>
       </c>
       <c r="G4" t="s">
         <v>19</v>
@@ -672,10 +672,10 @@
         <v>2015</v>
       </c>
       <c r="E5">
-        <v>0.331800607350954</v>
+        <v>0.307028531041414</v>
       </c>
       <c r="F5">
-        <v>1.99351237711982</v>
+        <v>2.1848306953316</v>
       </c>
       <c r="G5" t="s">
         <v>22</v>
@@ -701,10 +701,10 @@
         <v>2015</v>
       </c>
       <c r="E6">
-        <v>0.355265260926627</v>
+        <v>0.349008347894633</v>
       </c>
       <c r="F6">
-        <v>1.55760283043896</v>
+        <v>1.5543215378215</v>
       </c>
       <c r="G6" t="s">
         <v>25</v>
@@ -730,10 +730,10 @@
         <v>2015</v>
       </c>
       <c r="E7">
-        <v>0.324523936230862</v>
+        <v>0.320247224943911</v>
       </c>
       <c r="F7">
-        <v>1.64071462605627</v>
+        <v>1.66930074309966</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -759,10 +759,10 @@
         <v>2015</v>
       </c>
       <c r="E8">
-        <v>0.493045073236842</v>
+        <v>0.503753273418367</v>
       </c>
       <c r="F8">
-        <v>0.799173067176846</v>
+        <v>0.7707488410958</v>
       </c>
       <c r="G8" t="s">
         <v>31</v>
@@ -788,10 +788,10 @@
         <v>2015</v>
       </c>
       <c r="E9">
-        <v>0.429424708773333</v>
+        <v>0.425382594280401</v>
       </c>
       <c r="F9">
-        <v>1.08792405246637</v>
+        <v>1.0281129827989</v>
       </c>
       <c r="G9" t="s">
         <v>35</v>
@@ -817,10 +817,10 @@
         <v>2015</v>
       </c>
       <c r="E10">
-        <v>0.406670666707175</v>
+        <v>0.411499013714513</v>
       </c>
       <c r="F10">
-        <v>1.17165489763336</v>
+        <v>1.10379245748739</v>
       </c>
       <c r="G10" t="s">
         <v>38</v>
@@ -846,10 +846,10 @@
         <v>2015</v>
       </c>
       <c r="E11">
-        <v>0.395638377269365</v>
+        <v>0.39978333630301</v>
       </c>
       <c r="F11">
-        <v>1.09227006120085</v>
+        <v>1.06587278526221</v>
       </c>
       <c r="G11" t="s">
         <v>41</v>
@@ -875,10 +875,10 @@
         <v>2015</v>
       </c>
       <c r="E12">
-        <v>0.567018154845911</v>
+        <v>0.539980070771243</v>
       </c>
       <c r="F12">
-        <v>0.647342879668618</v>
+        <v>0.6841514493298</v>
       </c>
       <c r="G12" t="s">
         <v>44</v>
@@ -904,10 +904,10 @@
         <v>2015</v>
       </c>
       <c r="E13">
-        <v>0.504707780365601</v>
+        <v>0.466433848116679</v>
       </c>
       <c r="F13">
-        <v>0.870895309456587</v>
+        <v>0.857110761360936</v>
       </c>
       <c r="G13" t="s">
         <v>47</v>
@@ -933,10 +933,10 @@
         <v>2015</v>
       </c>
       <c r="E14">
-        <v>0.350802761003074</v>
+        <v>0.343539848957927</v>
       </c>
       <c r="F14">
-        <v>1.59775147419397</v>
+        <v>1.5935056680588</v>
       </c>
       <c r="G14" t="s">
         <v>50</v>
@@ -962,10 +962,10 @@
         <v>2015</v>
       </c>
       <c r="E15">
-        <v>0.315722312545943</v>
+        <v>0.311233851578991</v>
       </c>
       <c r="F15">
-        <v>1.71464749361646</v>
+        <v>1.76364975957949</v>
       </c>
       <c r="G15" t="s">
         <v>53</v>
@@ -991,10 +991,10 @@
         <v>2015</v>
       </c>
       <c r="E16">
-        <v>0.50558228969071</v>
+        <v>0.470517586492642</v>
       </c>
       <c r="F16">
-        <v>0.814368661622665</v>
+        <v>0.836152485801508</v>
       </c>
       <c r="G16" t="s">
         <v>56</v>
@@ -1020,10 +1020,10 @@
         <v>2015</v>
       </c>
       <c r="E17">
-        <v>0.398600571700721</v>
+        <v>0.390814793086742</v>
       </c>
       <c r="F17">
-        <v>1.17090878966136</v>
+        <v>1.23447676245225</v>
       </c>
       <c r="G17" t="s">
         <v>59</v>

--- a/Catch models/management_table_macarellus_cmsy.xlsx
+++ b/Catch models/management_table_macarellus_cmsy.xlsx
@@ -52,151 +52,151 @@
     <t>NN_CMSY_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.31 (0.24-0.39)</t>
-  </si>
-  <si>
-    <t>2.01 (1.19-3.36)</t>
-  </si>
-  <si>
-    <t>Overfished and overfishing</t>
+    <t>0.27 (0.09-0.51)</t>
+  </si>
+  <si>
+    <t>0.87 (0.23-6.93)</t>
+  </si>
+  <si>
+    <t>Overfished but not overfishing</t>
   </si>
   <si>
     <t>NN_CMSY_Higher resilience</t>
   </si>
   <si>
-    <t>0.30 (0.26-0.35)</t>
-  </si>
-  <si>
-    <t>1.87 (1.34-2.54)</t>
+    <t>0.26 (0.10-0.53)</t>
+  </si>
+  <si>
+    <t>0.81 (0.20-6.04)</t>
   </si>
   <si>
     <t>NN_CMSY_lower resilience</t>
   </si>
   <si>
-    <t>0.35 (0.20-0.59)</t>
-  </si>
-  <si>
-    <t>1.51 (0.53-4.79)</t>
+    <t>0.33 (0.16-0.60)</t>
+  </si>
+  <si>
+    <t>0.57 (0.18-2.71)</t>
   </si>
   <si>
     <t>NN_CMSY_Non-informative_r</t>
   </si>
   <si>
-    <t>0.31 (0.21-0.43)</t>
-  </si>
-  <si>
-    <t>2.18 (1.00-4.88)</t>
+    <t>0.30 (0.12-0.54)</t>
+  </si>
+  <si>
+    <t>0.72 (0.22-4.98)</t>
   </si>
   <si>
     <t>Target_switch_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.35 (0.25-0.57)</t>
-  </si>
-  <si>
-    <t>1.55 (0.62-3.15)</t>
+    <t>0.56 (0.12-1.00)</t>
+  </si>
+  <si>
+    <t>0.23 (0.10-4.29)</t>
   </si>
   <si>
     <t>Target_switch_Higher resilience</t>
   </si>
   <si>
-    <t>0.32 (0.27-0.41)</t>
-  </si>
-  <si>
-    <t>1.67 (1.00-2.35)</t>
+    <t>0.45 (0.07-1.01)</t>
+  </si>
+  <si>
+    <t>0.28 (0.10-11.57)</t>
   </si>
   <si>
     <t>Target_switch_lower resilience</t>
   </si>
   <si>
-    <t>0.50 (0.24-0.79)</t>
-  </si>
-  <si>
-    <t>0.77 (0.37-3.32)</t>
-  </si>
-  <si>
-    <t>Overfished but not overfishing</t>
+    <t>0.55 (0.24-0.90)</t>
+  </si>
+  <si>
+    <t>0.22 (0.10-1.13)</t>
   </si>
   <si>
     <t>Target_switch_Non-informative_r</t>
   </si>
   <si>
-    <t>0.43 (0.23-0.70)</t>
-  </si>
-  <si>
-    <t>1.03 (0.45-3.41)</t>
+    <t>0.56 (0.19-0.95)</t>
+  </si>
+  <si>
+    <t>0.23 (0.11-1.76)</t>
   </si>
   <si>
     <t>Uninformative_bk_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.41 (0.26-0.71)</t>
-  </si>
-  <si>
-    <t>1.10 (0.45-2.78)</t>
+    <t>0.78 (0.15-1.34)</t>
+  </si>
+  <si>
+    <t>0.16 (0.08-2.63)</t>
   </si>
   <si>
     <t>Uninformative_bk_Higher resilience</t>
   </si>
   <si>
-    <t>0.40 (0.28-0.63)</t>
-  </si>
-  <si>
-    <t>1.07 (0.49-2.16)</t>
+    <t>1.00 (0.11-1.69)</t>
+  </si>
+  <si>
+    <t>0.11 (0.06-4.25)</t>
+  </si>
+  <si>
+    <t>Neither overfishing nor overfished</t>
   </si>
   <si>
     <t>Uninformative_bk_lower resilience</t>
   </si>
   <si>
-    <t>0.54 (0.26-0.87)</t>
-  </si>
-  <si>
-    <t>0.68 (0.32-2.95)</t>
+    <t>0.64 (0.23-1.18)</t>
+  </si>
+  <si>
+    <t>0.17 (0.07-1.04)</t>
   </si>
   <si>
     <t>Uninformative_bk_Non-informative_r</t>
   </si>
   <si>
-    <t>0.47 (0.24-0.78)</t>
-  </si>
-  <si>
-    <t>0.86 (0.39-3.18)</t>
+    <t>0.67 (0.21-1.18)</t>
+  </si>
+  <si>
+    <t>0.19 (0.08-1.51)</t>
   </si>
   <si>
     <t>zBRT_Euler-lotka methods</t>
   </si>
   <si>
-    <t>0.34 (0.25-0.49)</t>
-  </si>
-  <si>
-    <t>1.59 (0.77-3.08)</t>
+    <t>0.40 (0.12-0.82)</t>
+  </si>
+  <si>
+    <t>0.40 (0.14-4.41)</t>
   </si>
   <si>
     <t>zBRT_Higher resilience</t>
   </si>
   <si>
-    <t>0.31 (0.26-0.38)</t>
-  </si>
-  <si>
-    <t>1.76 (1.14-2.49)</t>
+    <t>0.39 (0.09-0.99)</t>
+  </si>
+  <si>
+    <t>0.37 (0.11-6.43)</t>
   </si>
   <si>
     <t>zBRT_lower resilience</t>
   </si>
   <si>
-    <t>0.47 (0.26-0.75)</t>
-  </si>
-  <si>
-    <t>0.84 (0.38-2.81)</t>
+    <t>0.52 (0.20-0.90)</t>
+  </si>
+  <si>
+    <t>0.25 (0.11-1.68)</t>
   </si>
   <si>
     <t>zBRT_Non-informative_r</t>
   </si>
   <si>
-    <t>0.39 (0.24-0.64)</t>
-  </si>
-  <si>
-    <t>1.23 (0.51-3.30)</t>
+    <t>0.45 (0.19-0.84)</t>
+  </si>
+  <si>
+    <t>0.33 (0.13-1.93)</t>
   </si>
 </sst>
 </file>
@@ -582,13 +582,13 @@
         <v>11</v>
       </c>
       <c r="D2">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E2">
-        <v>0.308984125884021</v>
+        <v>0.266303951561274</v>
       </c>
       <c r="F2">
-        <v>2.00862768631171</v>
+        <v>0.8670808383108281</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -611,13 +611,13 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E3">
-        <v>0.302531754103853</v>
+        <v>0.263298039493454</v>
       </c>
       <c r="F3">
-        <v>1.87164011037127</v>
+        <v>0.809412226015187</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -640,13 +640,13 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E4">
-        <v>0.350896408871818</v>
+        <v>0.33042124783202</v>
       </c>
       <c r="F4">
-        <v>1.50649917333501</v>
+        <v>0.568003103942048</v>
       </c>
       <c r="G4" t="s">
         <v>19</v>
@@ -669,13 +669,13 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E5">
-        <v>0.307028531041414</v>
+        <v>0.304408155614677</v>
       </c>
       <c r="F5">
-        <v>2.1848306953316</v>
+        <v>0.722072275311281</v>
       </c>
       <c r="G5" t="s">
         <v>22</v>
@@ -698,13 +698,13 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E6">
-        <v>0.349008347894633</v>
+        <v>0.555173185917759</v>
       </c>
       <c r="F6">
-        <v>1.5543215378215</v>
+        <v>0.228520515609581</v>
       </c>
       <c r="G6" t="s">
         <v>25</v>
@@ -727,13 +727,13 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E7">
-        <v>0.320247224943911</v>
+        <v>0.445448870887135</v>
       </c>
       <c r="F7">
-        <v>1.66930074309966</v>
+        <v>0.281060838710632</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -756,13 +756,13 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E8">
-        <v>0.503753273418367</v>
+        <v>0.550655321616103</v>
       </c>
       <c r="F8">
-        <v>0.7707488410958</v>
+        <v>0.222827634236926</v>
       </c>
       <c r="G8" t="s">
         <v>31</v>
@@ -771,7 +771,7 @@
         <v>32</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -782,22 +782,22 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9">
+        <v>2023</v>
+      </c>
+      <c r="E9">
+        <v>0.555583875124694</v>
+      </c>
+      <c r="F9">
+        <v>0.231390853025768</v>
+      </c>
+      <c r="G9" t="s">
         <v>34</v>
       </c>
-      <c r="D9">
-        <v>2015</v>
-      </c>
-      <c r="E9">
-        <v>0.425382594280401</v>
-      </c>
-      <c r="F9">
-        <v>1.0281129827989</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>35</v>
-      </c>
-      <c r="H9" t="s">
-        <v>36</v>
       </c>
       <c r="I9" t="s">
         <v>14</v>
@@ -811,22 +811,22 @@
         <v>10</v>
       </c>
       <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10">
+        <v>2023</v>
+      </c>
+      <c r="E10">
+        <v>0.775634495510379</v>
+      </c>
+      <c r="F10">
+        <v>0.158728896499541</v>
+      </c>
+      <c r="G10" t="s">
         <v>37</v>
       </c>
-      <c r="D10">
-        <v>2015</v>
-      </c>
-      <c r="E10">
-        <v>0.411499013714513</v>
-      </c>
-      <c r="F10">
-        <v>1.10379245748739</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>38</v>
-      </c>
-      <c r="H10" t="s">
-        <v>39</v>
       </c>
       <c r="I10" t="s">
         <v>14</v>
@@ -840,25 +840,25 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11">
+        <v>2023</v>
+      </c>
+      <c r="E11">
+        <v>1.00423228462928</v>
+      </c>
+      <c r="F11">
+        <v>0.113898228280344</v>
+      </c>
+      <c r="G11" t="s">
         <v>40</v>
       </c>
-      <c r="D11">
-        <v>2015</v>
-      </c>
-      <c r="E11">
-        <v>0.39978333630301</v>
-      </c>
-      <c r="F11">
-        <v>1.06587278526221</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>41</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>42</v>
-      </c>
-      <c r="I11" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -872,13 +872,13 @@
         <v>43</v>
       </c>
       <c r="D12">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E12">
-        <v>0.539980070771243</v>
+        <v>0.641147502160936</v>
       </c>
       <c r="F12">
-        <v>0.6841514493298</v>
+        <v>0.170203922057932</v>
       </c>
       <c r="G12" t="s">
         <v>44</v>
@@ -887,7 +887,7 @@
         <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -901,13 +901,13 @@
         <v>46</v>
       </c>
       <c r="D13">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E13">
-        <v>0.466433848116679</v>
+        <v>0.674586997685466</v>
       </c>
       <c r="F13">
-        <v>0.857110761360936</v>
+        <v>0.185441246419058</v>
       </c>
       <c r="G13" t="s">
         <v>47</v>
@@ -916,7 +916,7 @@
         <v>48</v>
       </c>
       <c r="I13" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -930,13 +930,13 @@
         <v>49</v>
       </c>
       <c r="D14">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E14">
-        <v>0.343539848957927</v>
+        <v>0.397443028011084</v>
       </c>
       <c r="F14">
-        <v>1.5935056680588</v>
+        <v>0.395934188283469</v>
       </c>
       <c r="G14" t="s">
         <v>50</v>
@@ -959,13 +959,13 @@
         <v>52</v>
       </c>
       <c r="D15">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E15">
-        <v>0.311233851578991</v>
+        <v>0.387535458690153</v>
       </c>
       <c r="F15">
-        <v>1.76364975957949</v>
+        <v>0.372342111460795</v>
       </c>
       <c r="G15" t="s">
         <v>53</v>
@@ -988,13 +988,13 @@
         <v>55</v>
       </c>
       <c r="D16">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E16">
-        <v>0.470517586492642</v>
+        <v>0.524907852034578</v>
       </c>
       <c r="F16">
-        <v>0.836152485801508</v>
+        <v>0.252543334467288</v>
       </c>
       <c r="G16" t="s">
         <v>56</v>
@@ -1003,7 +1003,7 @@
         <v>57</v>
       </c>
       <c r="I16" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1017,13 +1017,13 @@
         <v>58</v>
       </c>
       <c r="D17">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E17">
-        <v>0.390814793086742</v>
+        <v>0.454071689652408</v>
       </c>
       <c r="F17">
-        <v>1.23447676245225</v>
+        <v>0.330061335101592</v>
       </c>
       <c r="G17" t="s">
         <v>59</v>
